--- a/data/trans_dic/P2C_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,5; 22,69</t>
+          <t>15,25; 22,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,16; 39,32</t>
+          <t>30,57; 39,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,86; 27,57</t>
+          <t>19,05; 27,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 11,28</t>
+          <t>3,53; 10,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,65; 24,85</t>
+          <t>17,58; 24,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,79; 50,43</t>
+          <t>40,97; 50,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,89; 37,16</t>
+          <t>27,48; 36,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,96; 14,23</t>
+          <t>5,99; 13,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 22,74</t>
+          <t>17,92; 22,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,68; 43,54</t>
+          <t>36,63; 43,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,49; 30,52</t>
+          <t>24,58; 30,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,68</t>
+          <t>5,33; 10,8</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,37; 33,25</t>
+          <t>26,55; 33,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,47; 43,12</t>
+          <t>35,32; 43,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,3; 42,05</t>
+          <t>34,0; 42,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,3; 16,71</t>
+          <t>8,43; 16,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,05; 55,44</t>
+          <t>47,58; 55,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,97; 70,07</t>
+          <t>62,26; 70,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,13; 61,38</t>
+          <t>53,78; 61,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 22,72</t>
+          <t>10,98; 22,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,92; 42,29</t>
+          <t>36,87; 42,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,3; 55,03</t>
+          <t>48,94; 54,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,75; 50,55</t>
+          <t>45,02; 50,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 18,44</t>
+          <t>11,53; 18,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,55; 59,44</t>
+          <t>51,56; 59,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,54; 77,44</t>
+          <t>70,13; 77,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,5; 59,48</t>
+          <t>51,92; 59,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,88; 24,55</t>
+          <t>16,73; 23,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,32; 63,13</t>
+          <t>55,04; 63,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,33; 84,44</t>
+          <t>78,6; 84,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,21; 69,07</t>
+          <t>62,39; 69,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 25,03</t>
+          <t>16,03; 25,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,41; 60,36</t>
+          <t>54,21; 59,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,57; 80,25</t>
+          <t>75,39; 80,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,03; 63,3</t>
+          <t>57,96; 63,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,8; 23,59</t>
+          <t>18,23; 23,78</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,33; 36,54</t>
+          <t>28,43; 36,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,29; 56,7</t>
+          <t>48,68; 57,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,99; 34,61</t>
+          <t>27,38; 34,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 14,88</t>
+          <t>4,39; 14,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,59; 29,6</t>
+          <t>21,67; 29,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,46; 49,17</t>
+          <t>40,73; 49,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,47; 34,57</t>
+          <t>27,25; 34,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 16,12</t>
+          <t>11,46; 16,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,01; 31,94</t>
+          <t>25,94; 31,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,64; 51,68</t>
+          <t>45,66; 51,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,65; 33,68</t>
+          <t>28,43; 33,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,45</t>
+          <t>7,22; 14,5</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,58</t>
+          <t>8,45; 15,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,79; 31,62</t>
+          <t>22,37; 31,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,0; 16,6</t>
+          <t>10,17; 16,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,37</t>
+          <t>6,6; 11,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 22,7</t>
+          <t>14,9; 22,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,57; 27,87</t>
+          <t>19,41; 28,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,58; 17,87</t>
+          <t>11,58; 18,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,48</t>
+          <t>8,61; 12,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,84; 17,94</t>
+          <t>12,77; 17,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,99; 28,25</t>
+          <t>22,0; 28,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,5; 16,11</t>
+          <t>11,46; 16,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 10,98</t>
+          <t>8,26; 11,12</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,6; 14,78</t>
+          <t>7,23; 14,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,44; 28,9</t>
+          <t>18,49; 28,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,33; 15,35</t>
+          <t>8,42; 15,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,95</t>
+          <t>6,19; 11,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,88; 21,52</t>
+          <t>13,92; 21,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,24; 30,84</t>
+          <t>21,35; 31,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,95; 21,46</t>
+          <t>13,12; 21,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,94; 75,48</t>
+          <t>10,87; 72,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,73; 16,94</t>
+          <t>11,67; 17,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,57; 28,51</t>
+          <t>21,85; 28,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,86; 17,2</t>
+          <t>12,01; 17,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 61,1</t>
+          <t>9,67; 61,96</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,05; 27,98</t>
+          <t>16,79; 27,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,18; 42,94</t>
+          <t>29,94; 43,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,22; 32,17</t>
+          <t>22,08; 32,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,98; 25,55</t>
+          <t>17,73; 25,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,27; 28,02</t>
+          <t>18,29; 27,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,71; 52,32</t>
+          <t>41,72; 52,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,75; 42,6</t>
+          <t>31,7; 42,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,64; 34,77</t>
+          <t>28,69; 35,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,18; 26,28</t>
+          <t>18,72; 25,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,93; 47,47</t>
+          <t>38,67; 46,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,04; 36,84</t>
+          <t>28,93; 36,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,23; 30,32</t>
+          <t>25,01; 29,94</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,44; 30,83</t>
+          <t>27,54; 30,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,15; 46,51</t>
+          <t>43,05; 46,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,7; 32,72</t>
+          <t>29,72; 32,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,38</t>
+          <t>9,34; 13,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,87; 36,05</t>
+          <t>32,93; 36,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,93; 53,43</t>
+          <t>49,94; 53,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,04; 40,48</t>
+          <t>37,14; 40,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,39; 36,32</t>
+          <t>16,32; 35,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,68; 32,91</t>
+          <t>30,84; 33,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46,82; 49,42</t>
+          <t>47,12; 49,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33,91; 36,26</t>
+          <t>33,92; 36,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,87; 26,0</t>
+          <t>13,97; 23,9</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76604; 112099</t>
+          <t>75327; 111840</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>136984; 178580</t>
+          <t>138836; 177567</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79095; 115640</t>
+          <t>79891; 115501</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14612; 45108</t>
+          <t>14111; 43783</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82496; 116174</t>
+          <t>82195; 116341</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>175486; 216974</t>
+          <t>176244; 218237</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>110390; 147077</t>
+          <t>108759; 146088</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18657; 44558</t>
+          <t>18763; 43770</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>167467; 218690</t>
+          <t>172292; 218323</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>324384; 385076</t>
+          <t>323957; 384039</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>199608; 248822</t>
+          <t>200421; 248461</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37520; 76195</t>
+          <t>38011; 77038</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>193929; 244548</t>
+          <t>195301; 243289</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>243738; 296298</t>
+          <t>242703; 295741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>202533; 248293</t>
+          <t>200762; 249065</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35169; 70795</t>
+          <t>35701; 70241</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>294287; 346783</t>
+          <t>297590; 347752</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>378169; 427622</t>
+          <t>379924; 430262</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>305024; 345923</t>
+          <t>303082; 349045</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56835; 116335</t>
+          <t>56223; 115964</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>502416; 575535</t>
+          <t>501775; 576442</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>639565; 713908</t>
+          <t>634901; 711735</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516464; 583412</t>
+          <t>519538; 583789</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>107795; 172518</t>
+          <t>107926; 172348</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>329247; 379604</t>
+          <t>329316; 378112</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>480962; 528066</t>
+          <t>478194; 528233</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>344588; 397978</t>
+          <t>347414; 397312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90542; 131671</t>
+          <t>89739; 128522</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>381548; 435437</t>
+          <t>379653; 434711</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>556790; 600242</t>
+          <t>558752; 600212</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>411477; 456837</t>
+          <t>412633; 458439</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97672; 148149</t>
+          <t>94878; 149633</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>722730; 801842</t>
+          <t>720191; 794270</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1052445; 1117603</t>
+          <t>1049964; 1117194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>772035; 842197</t>
+          <t>771137; 842149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>200869; 266166</t>
+          <t>205659; 268322</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>147052; 189707</t>
+          <t>147573; 191077</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>296807; 348496</t>
+          <t>299199; 352160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174350; 223628</t>
+          <t>176859; 223974</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40318; 132132</t>
+          <t>38988; 131477</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>111338; 152647</t>
+          <t>111746; 151052</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>249310; 302975</t>
+          <t>250994; 304327</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>178298; 224411</t>
+          <t>176894; 226630</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80750; 114888</t>
+          <t>81698; 116207</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>269140; 330493</t>
+          <t>268391; 327157</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>561705; 636093</t>
+          <t>562026; 637800</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>371093; 436240</t>
+          <t>368233; 435927</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>108971; 231340</t>
+          <t>115495; 232125</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33026; 60252</t>
+          <t>32691; 58563</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97884; 135774</t>
+          <t>96082; 133268</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47780; 79315</t>
+          <t>48611; 79370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38326; 63820</t>
+          <t>37023; 62705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59586; 91686</t>
+          <t>60192; 90837</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87615; 124815</t>
+          <t>86920; 125817</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57535; 88806</t>
+          <t>57522; 91967</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47204; 68362</t>
+          <t>47198; 68361</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>101502; 141841</t>
+          <t>100949; 141829</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192866; 247794</t>
+          <t>192956; 248771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112083; 157071</t>
+          <t>111753; 157100</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89342; 121823</t>
+          <t>91610; 123387</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22223; 43251</t>
+          <t>21153; 42971</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57116; 89515</t>
+          <t>57269; 89821</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27850; 51326</t>
+          <t>28159; 50708</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23211; 40300</t>
+          <t>22792; 40616</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>47602; 73804</t>
+          <t>47742; 73481</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75201; 109180</t>
+          <t>75576; 110030</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48909; 81052</t>
+          <t>49566; 79536</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66540; 459184</t>
+          <t>66122; 441477</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>74537; 107629</t>
+          <t>74144; 109510</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>143181; 189235</t>
+          <t>145053; 189379</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>84468; 122490</t>
+          <t>85533; 122046</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93939; 596677</t>
+          <t>94416; 605054</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>35779; 58734</t>
+          <t>35237; 57578</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>75401; 107285</t>
+          <t>74812; 108801</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57106; 82676</t>
+          <t>56749; 82461</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50852; 72249</t>
+          <t>50132; 72114</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>61002; 93560</t>
+          <t>61071; 92110</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>162253; 203499</t>
+          <t>162267; 205188</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>127043; 170474</t>
+          <t>126862; 169291</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>121947; 148074</t>
+          <t>122161; 150467</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>104281; 142929</t>
+          <t>101796; 140613</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>248671; 303228</t>
+          <t>247016; 298899</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190812; 242130</t>
+          <t>190109; 243085</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>178807; 214862</t>
+          <t>177202; 212137</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>899229; 1010203</t>
+          <t>902370; 1007998</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1478659; 1593946</t>
+          <t>1475400; 1592229</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1007995; 1110714</t>
+          <t>1008815; 1117687</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>332435; 462865</t>
+          <t>323099; 461845</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1110807; 1218215</t>
+          <t>1112673; 1224850</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1776561; 1901319</t>
+          <t>1777181; 1901415</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1312864; 1434726</t>
+          <t>1316269; 1436404</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>608615; 1348448</t>
+          <t>605896; 1323806</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2042280; 2190236</t>
+          <t>2052399; 2205057</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3270192; 3452205</t>
+          <t>3291292; 3461983</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2353086; 2516177</t>
+          <t>2353450; 2514349</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>995109; 1864797</t>
+          <t>1002271; 1713776</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,25; 22,64</t>
+          <t>15,73; 22,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,57; 39,1</t>
+          <t>30,49; 39,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 27,54</t>
+          <t>18,57; 27,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,95</t>
+          <t>4,8; 12,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 24,89</t>
+          <t>17,5; 24,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,97; 50,73</t>
+          <t>41,12; 50,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,48; 36,91</t>
+          <t>27,79; 37,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 13,97</t>
+          <t>7,01; 16,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 22,71</t>
+          <t>17,65; 22,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,63; 43,42</t>
+          <t>36,67; 43,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,58; 30,48</t>
+          <t>24,42; 30,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,8</t>
+          <t>6,85; 12,96</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,55; 33,08</t>
+          <t>26,23; 33,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,32; 43,04</t>
+          <t>35,48; 42,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,0; 42,18</t>
+          <t>33,81; 42,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 16,58</t>
+          <t>9,86; 17,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,58; 55,6</t>
+          <t>47,09; 55,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,26; 70,51</t>
+          <t>62,28; 70,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,78; 61,94</t>
+          <t>53,92; 61,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 22,65</t>
+          <t>18,04; 25,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,87; 42,35</t>
+          <t>36,87; 42,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,94; 54,86</t>
+          <t>49,02; 54,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,02; 50,59</t>
+          <t>44,76; 50,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 18,42</t>
+          <t>14,93; 20,75</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,56; 59,2</t>
+          <t>50,86; 59,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,13; 77,47</t>
+          <t>70,63; 77,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,92; 59,38</t>
+          <t>51,38; 59,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,73; 23,96</t>
+          <t>17,47; 24,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,04; 63,03</t>
+          <t>54,89; 62,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,6; 84,44</t>
+          <t>78,18; 84,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,39; 69,31</t>
+          <t>61,95; 69,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 25,28</t>
+          <t>21,05; 26,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,21; 59,79</t>
+          <t>54,26; 59,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,39; 80,22</t>
+          <t>75,42; 80,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57,96; 63,3</t>
+          <t>57,85; 63,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 23,78</t>
+          <t>20,31; 25,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,43; 36,81</t>
+          <t>28,26; 36,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,68; 57,3</t>
+          <t>48,4; 56,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,38; 34,67</t>
+          <t>27,05; 34,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 14,81</t>
+          <t>11,95; 17,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 29,29</t>
+          <t>21,48; 29,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,73; 49,39</t>
+          <t>40,31; 49,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,25; 34,92</t>
+          <t>27,86; 34,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,46; 16,3</t>
+          <t>13,11; 17,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,94; 31,62</t>
+          <t>26,19; 31,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,66; 51,82</t>
+          <t>45,71; 51,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,43; 33,66</t>
+          <t>28,39; 34,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 14,5</t>
+          <t>13,32; 16,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,14</t>
+          <t>8,52; 15,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,37; 31,03</t>
+          <t>22,84; 31,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,17; 16,61</t>
+          <t>9,88; 16,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,17</t>
+          <t>6,76; 10,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,9; 22,49</t>
+          <t>14,96; 22,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,41; 28,1</t>
+          <t>19,3; 28,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,58; 18,51</t>
+          <t>11,54; 18,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,48</t>
+          <t>8,77; 12,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,94</t>
+          <t>12,92; 18,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,0; 28,36</t>
+          <t>22,26; 28,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,46; 16,12</t>
+          <t>11,7; 16,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 11,12</t>
+          <t>8,15; 11,09</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 14,69</t>
+          <t>7,28; 14,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,49; 28,99</t>
+          <t>18,77; 28,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,42; 15,17</t>
+          <t>8,09; 15,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,03</t>
+          <t>6,51; 11,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,92; 21,43</t>
+          <t>13,62; 21,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,35; 31,08</t>
+          <t>21,53; 30,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,12; 21,05</t>
+          <t>13,23; 21,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 72,57</t>
+          <t>9,8; 14,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,67; 17,23</t>
+          <t>11,5; 17,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,85; 28,53</t>
+          <t>21,75; 28,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,14</t>
+          <t>11,83; 17,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,67; 61,96</t>
+          <t>8,78; 12,03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,79; 27,43</t>
+          <t>17,03; 28,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,94; 43,55</t>
+          <t>30,01; 43,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,08; 32,09</t>
+          <t>22,02; 31,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,73; 25,5</t>
+          <t>17,03; 24,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 27,59</t>
+          <t>18,29; 28,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,72; 52,75</t>
+          <t>42,07; 52,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,7; 42,3</t>
+          <t>31,07; 41,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,69; 35,33</t>
+          <t>28,15; 34,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,72; 25,86</t>
+          <t>19,09; 26,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,67; 46,79</t>
+          <t>38,5; 47,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28,93; 36,99</t>
+          <t>28,9; 36,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,01; 29,94</t>
+          <t>24,78; 29,58</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,76</t>
+          <t>27,69; 30,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,05; 46,46</t>
+          <t>43,01; 46,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,72; 32,93</t>
+          <t>29,68; 32,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,35</t>
+          <t>12,4; 14,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,93; 36,25</t>
+          <t>32,84; 36,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,94; 53,44</t>
+          <t>49,9; 53,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,14; 40,52</t>
+          <t>37,04; 40,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,32; 35,66</t>
+          <t>16,95; 19,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,84; 33,13</t>
+          <t>30,74; 33,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,12; 49,56</t>
+          <t>47,08; 49,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,24</t>
+          <t>33,89; 36,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,97; 23,9</t>
+          <t>15,09; 16,8</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>72427</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75327; 111840</t>
+          <t>77735; 111714</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>138836; 177567</t>
+          <t>138483; 178765</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79891; 115501</t>
+          <t>77893; 115019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14111; 43783</t>
+          <t>19573; 52184</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82195; 116341</t>
+          <t>81793; 116686</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>176244; 218237</t>
+          <t>176910; 218555</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>108759; 146088</t>
+          <t>109970; 146423</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18763; 43770</t>
+          <t>25398; 58267</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>172292; 218323</t>
+          <t>169742; 218647</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>323957; 384039</t>
+          <t>324314; 382744</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>200421; 248461</t>
+          <t>199042; 246433</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38011; 77038</t>
+          <t>52778; 99815</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49953</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93048</t>
+          <t>107801</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>143001</t>
+          <t>172172</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>195301; 243289</t>
+          <t>192933; 244355</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>242703; 295741</t>
+          <t>243779; 295219</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>200762; 249065</t>
+          <t>199641; 250096</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35701; 70241</t>
+          <t>47005; 85685</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>297590; 347752</t>
+          <t>294560; 346471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>379924; 430262</t>
+          <t>380079; 428704</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>303082; 349045</t>
+          <t>303859; 348782</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56223; 115964</t>
+          <t>90507; 127126</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501775; 576442</t>
+          <t>501838; 576195</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>634901; 711735</t>
+          <t>635973; 709285</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>519538; 583789</t>
+          <t>516595; 582935</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>107926; 172348</t>
+          <t>146120; 203108</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108561</t>
+          <t>128750</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>129079</t>
+          <t>150164</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>237640</t>
+          <t>278913</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>329316; 378112</t>
+          <t>324855; 378047</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>478194; 528233</t>
+          <t>481611; 528056</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>347414; 397312</t>
+          <t>343760; 395827</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89739; 128522</t>
+          <t>108480; 152596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>379653; 434711</t>
+          <t>378614; 431572</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>558752; 600212</t>
+          <t>555749; 600116</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>412633; 458439</t>
+          <t>409711; 456956</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94878; 149633</t>
+          <t>131176; 168149</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>720191; 794270</t>
+          <t>720843; 796665</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1049964; 1117194</t>
+          <t>1050371; 1115114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>771137; 842149</t>
+          <t>769745; 840933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>205659; 268322</t>
+          <t>252706; 311489</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88710</t>
+          <t>103116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>98556</t>
+          <t>112364</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>187266</t>
+          <t>215480</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>147573; 191077</t>
+          <t>146702; 191343</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>299199; 352160</t>
+          <t>297472; 349460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>176859; 223974</t>
+          <t>174767; 225857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38988; 131477</t>
+          <t>83716; 124439</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>111746; 151052</t>
+          <t>110736; 151882</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>250994; 304327</t>
+          <t>248361; 302812</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>176894; 226630</t>
+          <t>180850; 226202</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81698; 116207</t>
+          <t>96606; 127817</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>268391; 327157</t>
+          <t>270963; 326819</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>562026; 637800</t>
+          <t>562584; 638335</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>368233; 435927</t>
+          <t>367744; 440344</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>115495; 232125</t>
+          <t>191491; 240853</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48449</t>
+          <t>51966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>56686</t>
+          <t>64623</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>105135</t>
+          <t>116589</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32691; 58563</t>
+          <t>32934; 59949</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96082; 133268</t>
+          <t>98064; 136247</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48611; 79370</t>
+          <t>47219; 78745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37023; 62705</t>
+          <t>41166; 66640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60192; 90837</t>
+          <t>60435; 90405</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86920; 125817</t>
+          <t>86437; 125884</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57522; 91967</t>
+          <t>57314; 91531</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47198; 68361</t>
+          <t>53424; 77607</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100949; 141829</t>
+          <t>102123; 142672</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192956; 248771</t>
+          <t>195265; 249010</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111753; 157100</t>
+          <t>114013; 157815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91610; 123387</t>
+          <t>99258; 135083</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>252021</t>
+          <t>52390</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>283394</t>
+          <t>87042</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21153; 42971</t>
+          <t>21309; 42806</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57269; 89821</t>
+          <t>58134; 89488</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28159; 50708</t>
+          <t>27045; 50155</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22792; 40616</t>
+          <t>26506; 45498</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>47742; 73481</t>
+          <t>46722; 72726</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75576; 110030</t>
+          <t>76223; 109289</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49566; 79536</t>
+          <t>49965; 80976</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66122; 441477</t>
+          <t>43033; 62874</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>74144; 109510</t>
+          <t>73076; 108040</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>145053; 189379</t>
+          <t>144379; 189787</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85533; 122046</t>
+          <t>84240; 122041</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>94416; 605054</t>
+          <t>74334; 101818</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60264</t>
+          <t>64218</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>134874</t>
+          <t>145788</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>195138</t>
+          <t>210005</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>35237; 57578</t>
+          <t>35737; 59088</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>74812; 108801</t>
+          <t>74973; 108689</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56749; 82461</t>
+          <t>56589; 81785</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50132; 72114</t>
+          <t>52824; 77076</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>61071; 92110</t>
+          <t>61063; 94679</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>162267; 205188</t>
+          <t>163641; 204190</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>126862; 169291</t>
+          <t>124324; 167039</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>122161; 150467</t>
+          <t>130806; 160757</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>101796; 140613</t>
+          <t>103832; 143796</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>247016; 298899</t>
+          <t>245954; 300303</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190109; 243085</t>
+          <t>189896; 242485</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>177202; 212137</t>
+          <t>191982; 229185</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>412934</t>
+          <t>478875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>793292</t>
+          <t>673754</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1206225</t>
+          <t>1152629</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>902370; 1007998</t>
+          <t>907289; 1008885</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1475400; 1592229</t>
+          <t>1473734; 1595276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1008815; 1117687</t>
+          <t>1007320; 1112032</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>323099; 461845</t>
+          <t>438065; 523629</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1112673; 1224850</t>
+          <t>1109829; 1221313</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1777181; 1901415</t>
+          <t>1775443; 1895160</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1316269; 1436404</t>
+          <t>1312919; 1430779</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>605896; 1323806</t>
+          <t>633462; 716404</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2052399; 2205057</t>
+          <t>2046214; 2200666</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3291292; 3461983</t>
+          <t>3288658; 3459538</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2353450; 2514349</t>
+          <t>2351851; 2520436</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1002271; 1713776</t>
+          <t>1096644; 1221522</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
